--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,414 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123286570</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79883</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Marjamägg, Marjamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>491386</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6840654</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123286514</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79876</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Marjamägg, Marjamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>491451</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6840654</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123286669</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Marjamägg, Marjamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>491313</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6840661</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123286645</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Marjamägg, Marjamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>491353</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6840652</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286570</v>
+        <v>123286669</v>
       </c>
       <c r="B4" t="n">
-        <v>79883</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491386</v>
+        <v>491313</v>
       </c>
       <c r="R4" t="n">
-        <v>6840654</v>
+        <v>6840661</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286514</v>
+        <v>123286645</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491451</v>
+        <v>491353</v>
       </c>
       <c r="R5" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286669</v>
+        <v>123286514</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491313</v>
+        <v>491451</v>
       </c>
       <c r="R6" t="n">
-        <v>6840661</v>
+        <v>6840654</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286645</v>
+        <v>123286570</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491353</v>
+        <v>491386</v>
       </c>
       <c r="R7" t="n">
-        <v>6840652</v>
+        <v>6840654</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>123286669</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286645</v>
+        <v>123286570</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491353</v>
+        <v>491386</v>
       </c>
       <c r="R5" t="n">
-        <v>6840652</v>
+        <v>6840654</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286514</v>
+        <v>123286645</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491451</v>
+        <v>491353</v>
       </c>
       <c r="R6" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286570</v>
+        <v>123286514</v>
       </c>
       <c r="B7" t="n">
-        <v>79883</v>
+        <v>79879</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491386</v>
+        <v>491451</v>
       </c>
       <c r="R7" t="n">
         <v>6840654</v>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286669</v>
+        <v>123286514</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>79881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491313</v>
+        <v>491451</v>
       </c>
       <c r="R4" t="n">
-        <v>6840661</v>
+        <v>6840654</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286570</v>
+        <v>123286645</v>
       </c>
       <c r="B5" t="n">
-        <v>79886</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491386</v>
+        <v>491353</v>
       </c>
       <c r="R5" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286645</v>
+        <v>123286570</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>79888</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491353</v>
+        <v>491386</v>
       </c>
       <c r="R6" t="n">
-        <v>6840652</v>
+        <v>6840654</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286514</v>
+        <v>123286669</v>
       </c>
       <c r="B7" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491451</v>
+        <v>491313</v>
       </c>
       <c r="R7" t="n">
-        <v>6840654</v>
+        <v>6840661</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286514</v>
+        <v>123286645</v>
       </c>
       <c r="B4" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491451</v>
+        <v>491353</v>
       </c>
       <c r="R4" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286645</v>
+        <v>123286570</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>79889</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491353</v>
+        <v>491386</v>
       </c>
       <c r="R5" t="n">
-        <v>6840652</v>
+        <v>6840654</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286570</v>
+        <v>123286669</v>
       </c>
       <c r="B6" t="n">
-        <v>79888</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491386</v>
+        <v>491313</v>
       </c>
       <c r="R6" t="n">
-        <v>6840654</v>
+        <v>6840661</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286669</v>
+        <v>123286514</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491313</v>
+        <v>491451</v>
       </c>
       <c r="R7" t="n">
-        <v>6840661</v>
+        <v>6840654</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286645</v>
+        <v>123286669</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491353</v>
+        <v>491313</v>
       </c>
       <c r="R4" t="n">
-        <v>6840652</v>
+        <v>6840661</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286570</v>
+        <v>123286514</v>
       </c>
       <c r="B5" t="n">
-        <v>79889</v>
+        <v>79885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491386</v>
+        <v>491451</v>
       </c>
       <c r="R5" t="n">
         <v>6840654</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286669</v>
+        <v>123286570</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491313</v>
+        <v>491386</v>
       </c>
       <c r="R6" t="n">
-        <v>6840661</v>
+        <v>6840654</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286514</v>
+        <v>123286645</v>
       </c>
       <c r="B7" t="n">
-        <v>79882</v>
+        <v>78775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491451</v>
+        <v>491353</v>
       </c>
       <c r="R7" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286669</v>
+        <v>123286645</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491313</v>
+        <v>491353</v>
       </c>
       <c r="R4" t="n">
-        <v>6840661</v>
+        <v>6840652</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,12 +987,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
         <v>123286514</v>
       </c>
       <c r="B5" t="n">
-        <v>79885</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>123286570</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>79898</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286645</v>
+        <v>123286669</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491353</v>
+        <v>491313</v>
       </c>
       <c r="R7" t="n">
-        <v>6840652</v>
+        <v>6840661</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286645</v>
+        <v>123286669</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491353</v>
+        <v>491313</v>
       </c>
       <c r="R4" t="n">
-        <v>6840652</v>
+        <v>6840661</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286514</v>
+        <v>123286645</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491451</v>
+        <v>491353</v>
       </c>
       <c r="R5" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286570</v>
+        <v>123286514</v>
       </c>
       <c r="B6" t="n">
-        <v>79898</v>
+        <v>79896</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491386</v>
+        <v>491451</v>
       </c>
       <c r="R6" t="n">
         <v>6840654</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286669</v>
+        <v>123286570</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>79903</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491313</v>
+        <v>491386</v>
       </c>
       <c r="R7" t="n">
-        <v>6840661</v>
+        <v>6840654</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286669</v>
+        <v>123286570</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>79905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491313</v>
+        <v>491386</v>
       </c>
       <c r="R4" t="n">
-        <v>6840661</v>
+        <v>6840654</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286645</v>
+        <v>123286669</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491353</v>
+        <v>491313</v>
       </c>
       <c r="R5" t="n">
-        <v>6840652</v>
+        <v>6840661</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286514</v>
+        <v>123286645</v>
       </c>
       <c r="B6" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491451</v>
+        <v>491353</v>
       </c>
       <c r="R6" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286570</v>
+        <v>123286514</v>
       </c>
       <c r="B7" t="n">
-        <v>79903</v>
+        <v>79898</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491386</v>
+        <v>491451</v>
       </c>
       <c r="R7" t="n">
         <v>6840654</v>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286570</v>
+        <v>123286514</v>
       </c>
       <c r="B4" t="n">
-        <v>79905</v>
+        <v>79898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491386</v>
+        <v>491451</v>
       </c>
       <c r="R4" t="n">
         <v>6840654</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286669</v>
+        <v>123286570</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491313</v>
+        <v>491386</v>
       </c>
       <c r="R5" t="n">
-        <v>6840661</v>
+        <v>6840654</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,19 +1089,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286645</v>
+        <v>123286669</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491353</v>
+        <v>491313</v>
       </c>
       <c r="R6" t="n">
-        <v>6840652</v>
+        <v>6840661</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286514</v>
+        <v>123286645</v>
       </c>
       <c r="B7" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491451</v>
+        <v>491353</v>
       </c>
       <c r="R7" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286514</v>
+        <v>123286570</v>
       </c>
       <c r="B4" t="n">
-        <v>79898</v>
+        <v>79905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491451</v>
+        <v>491386</v>
       </c>
       <c r="R4" t="n">
         <v>6840654</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286570</v>
+        <v>123286514</v>
       </c>
       <c r="B5" t="n">
-        <v>79905</v>
+        <v>79898</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491386</v>
+        <v>491451</v>
       </c>
       <c r="R5" t="n">
         <v>6840654</v>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286570</v>
+        <v>123286645</v>
       </c>
       <c r="B4" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491386</v>
+        <v>491353</v>
       </c>
       <c r="R4" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286514</v>
+        <v>123286570</v>
       </c>
       <c r="B5" t="n">
-        <v>79898</v>
+        <v>79905</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491451</v>
+        <v>491386</v>
       </c>
       <c r="R5" t="n">
         <v>6840654</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286645</v>
+        <v>123286514</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491353</v>
+        <v>491451</v>
       </c>
       <c r="R7" t="n">
-        <v>6840652</v>
+        <v>6840654</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 45204-2023 artfynd.xlsx
+++ b/artfynd/A 45204-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286645</v>
+        <v>123286514</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491353</v>
+        <v>491451</v>
       </c>
       <c r="R4" t="n">
-        <v>6840652</v>
+        <v>6840654</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286570</v>
+        <v>123286645</v>
       </c>
       <c r="B5" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491386</v>
+        <v>491353</v>
       </c>
       <c r="R5" t="n">
-        <v>6840654</v>
+        <v>6840652</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286669</v>
+        <v>123286570</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491313</v>
+        <v>491386</v>
       </c>
       <c r="R6" t="n">
-        <v>6840661</v>
+        <v>6840654</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286514</v>
+        <v>123286669</v>
       </c>
       <c r="B7" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491451</v>
+        <v>491313</v>
       </c>
       <c r="R7" t="n">
-        <v>6840654</v>
+        <v>6840661</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,12 +1293,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
